--- a/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260913_noite.xlsx
+++ b/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260913_noite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\projetos\ofi\dados\SURVEY_VESSELS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CE3624-7EF6-479D-8485-AAC035B25F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AAFEEA0-53F8-4120-8651-102D22E79918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -239,9 +239,6 @@
     <t>status</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>Underway using Engine</t>
   </si>
   <si>
@@ -258,12 +255,19 @@
   </si>
   <si>
     <t>Class B</t>
+  </si>
+  <si>
+    <t>embarcacao</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000000"/>
+    <numFmt numFmtId="169" formatCode="#,##0.000000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -331,10 +335,10 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -972,13 +976,14 @@
     <col min="7" max="7" width="12.44140625" customWidth="1"/>
     <col min="8" max="8" width="23.33203125" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" customWidth="1"/>
     <col min="13" max="13" width="14.109375" customWidth="1"/>
     <col min="14" max="14" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="B1" t="s">
         <v>58</v>
@@ -1010,17 +1015,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="10">
-        <v>-24640833</v>
+      <c r="D2" s="9">
+        <v>-24.640833000000001</v>
       </c>
       <c r="E2" s="10">
-        <v>-42195835</v>
+        <v>-42.195835000000002</v>
       </c>
       <c r="F2" s="6">
         <v>46277.173611111109</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1032,17 +1037,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="10">
-        <v>-25570738</v>
-      </c>
-      <c r="E3" s="10">
-        <v>-42842857</v>
+      <c r="D3" s="9">
+        <v>-25.570737999999999</v>
+      </c>
+      <c r="E3">
+        <v>-42.842857000000002</v>
       </c>
       <c r="F3" s="6">
         <v>46277.427777777775</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1054,17 +1059,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="10">
-        <v>-23098541</v>
-      </c>
-      <c r="E4" s="10">
-        <v>-42777458</v>
+      <c r="D4" s="9">
+        <v>-23.098541000000001</v>
+      </c>
+      <c r="E4">
+        <v>-42.777458000000003</v>
       </c>
       <c r="F4" s="6">
         <v>46277.865972222222</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1076,17 +1081,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="10">
-        <v>-24659252</v>
-      </c>
-      <c r="E5" s="10">
-        <v>-42457294</v>
+      <c r="D5" s="9">
+        <v>-24.659251999999999</v>
+      </c>
+      <c r="E5">
+        <v>-42.457293999999997</v>
       </c>
       <c r="F5" s="6">
         <v>46275.42083333333</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1098,17 +1103,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="10">
-        <v>-22864473</v>
-      </c>
-      <c r="E6" s="10">
-        <v>-43109585</v>
+      <c r="D6" s="9">
+        <v>-22.864473</v>
+      </c>
+      <c r="E6">
+        <v>-43.109585000000003</v>
       </c>
       <c r="F6" s="6">
         <v>44390.56527777778</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1120,17 +1125,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="10">
-        <v>-22881845</v>
-      </c>
-      <c r="E7" s="10">
-        <v>-43117619</v>
+      <c r="D7" s="9">
+        <v>-22.881844999999998</v>
+      </c>
+      <c r="E7">
+        <v>-43.117618999999998</v>
       </c>
       <c r="F7" s="6">
         <v>46278.844444444447</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -1142,17 +1147,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="10">
-        <v>-22894632</v>
-      </c>
-      <c r="E8" s="10">
-        <v>-43212166</v>
+      <c r="D8" s="1">
+        <v>-22.894632000000001</v>
+      </c>
+      <c r="E8">
+        <v>-43.212166000000003</v>
       </c>
       <c r="F8" s="6">
         <v>46278.843055555553</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1164,17 +1169,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="10">
-        <v>-22848885</v>
-      </c>
-      <c r="E9" s="10">
-        <v>-43143326</v>
+      <c r="D9" s="1">
+        <v>-22.848884999999999</v>
+      </c>
+      <c r="E9">
+        <v>-43.143326000000002</v>
       </c>
       <c r="F9" s="6">
         <v>46278.845138888886</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I9" s="1"/>
     </row>
@@ -1186,17 +1191,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="10">
-        <v>-21924328</v>
-      </c>
-      <c r="E10" s="10">
-        <v>-39756535</v>
+      <c r="D10" s="1">
+        <v>-21.924327999999999</v>
+      </c>
+      <c r="E10">
+        <v>-39.756535</v>
       </c>
       <c r="F10" s="6">
         <v>46277.697222222225</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -1208,17 +1213,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="10">
-        <v>-23549366</v>
-      </c>
-      <c r="E11" s="10">
-        <v>-41096352</v>
+      <c r="D11" s="1">
+        <v>-23.549365999999999</v>
+      </c>
+      <c r="E11">
+        <v>-41.096352000000003</v>
       </c>
       <c r="F11" s="6">
         <v>46277.024305555555</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I11" s="1"/>
     </row>
@@ -1230,17 +1235,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="10">
-        <v>-22222944</v>
-      </c>
-      <c r="E12" s="10">
-        <v>-40309349</v>
+      <c r="D12" s="1">
+        <v>-22.222943999999998</v>
+      </c>
+      <c r="E12">
+        <v>-40.309348999999997</v>
       </c>
       <c r="F12" s="6">
         <v>46278.438194444447</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I12" s="1"/>
     </row>
@@ -1252,17 +1257,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="10">
-        <v>-21241184</v>
-      </c>
-      <c r="E13" s="10">
-        <v>-40035839</v>
+      <c r="D13" s="1">
+        <v>-21.241184000000001</v>
+      </c>
+      <c r="E13">
+        <v>-40.035839000000003</v>
       </c>
       <c r="F13" s="6">
         <v>46278.330555555556</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I13" s="1"/>
     </row>
@@ -1274,17 +1279,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="10">
-        <v>-21864485</v>
-      </c>
-      <c r="E14" s="10">
-        <v>-41016666</v>
+      <c r="D14" s="1">
+        <v>-21.864484999999998</v>
+      </c>
+      <c r="E14">
+        <v>-41.016666000000001</v>
       </c>
       <c r="F14" s="6">
         <v>46278.847222222219</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1296,17 +1301,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="10">
-        <v>-25021685</v>
-      </c>
-      <c r="E15" s="10">
-        <v>-42668240</v>
+      <c r="D15" s="1">
+        <v>-25.021685000000002</v>
+      </c>
+      <c r="E15">
+        <v>-42.668239999999997</v>
       </c>
       <c r="F15" s="6">
         <v>46277.431250000001</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -1318,17 +1323,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="10">
-        <v>-21214226</v>
-      </c>
-      <c r="E16" s="10">
-        <v>-39997829</v>
+      <c r="D16" s="1">
+        <v>-21.214226</v>
+      </c>
+      <c r="E16">
+        <v>-39.997829000000003</v>
       </c>
       <c r="F16" s="6">
         <v>46278.333333333336</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I16" s="1"/>
     </row>
@@ -1340,17 +1345,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="10">
-        <v>-30372272</v>
-      </c>
-      <c r="E17" s="10">
-        <v>-47695133</v>
+      <c r="D17" s="1">
+        <v>-30.372271999999999</v>
+      </c>
+      <c r="E17">
+        <v>-47.695132999999998</v>
       </c>
       <c r="F17" s="6">
         <v>44677.811111111114</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I17" s="1"/>
     </row>
@@ -1362,17 +1367,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="10">
-        <v>-22413794</v>
-      </c>
-      <c r="E18" s="10">
-        <v>-40920341</v>
+      <c r="D18" s="1">
+        <v>-22.413793999999999</v>
+      </c>
+      <c r="E18">
+        <v>-40.920341000000001</v>
       </c>
       <c r="F18" s="6">
         <v>46278.656944444447</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I18" s="1"/>
     </row>
@@ -1384,17 +1389,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C19" s="1"/>
-      <c r="D19" s="10">
-        <v>-22864527</v>
-      </c>
-      <c r="E19" s="10">
-        <v>-43111076</v>
+      <c r="D19" s="1">
+        <v>-22.864526999999999</v>
+      </c>
+      <c r="E19">
+        <v>-43.111075999999997</v>
       </c>
       <c r="F19" s="6">
         <v>45839.576388888891</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I19" s="1"/>
     </row>
@@ -1406,17 +1411,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="10">
-        <v>-24653959</v>
-      </c>
-      <c r="E20" s="10">
-        <v>-42235405</v>
+      <c r="D20" s="1">
+        <v>-24.653959</v>
+      </c>
+      <c r="E20">
+        <v>-42.235405</v>
       </c>
       <c r="F20" s="6">
         <v>46277.159722222219</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I20" s="1"/>
     </row>
@@ -1428,17 +1433,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C21" s="1"/>
-      <c r="D21" s="10">
-        <v>-23597019</v>
-      </c>
-      <c r="E21" s="10">
-        <v>-42626418</v>
+      <c r="D21" s="1">
+        <v>-23.597019</v>
+      </c>
+      <c r="E21">
+        <v>-42.626418000000001</v>
       </c>
       <c r="F21" s="6">
         <v>46278.845138888886</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I21" s="1"/>
     </row>
@@ -1450,17 +1455,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="9">
-        <v>7216545</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-55740231</v>
+      <c r="D22" s="7">
+        <v>7.216545</v>
+      </c>
+      <c r="E22">
+        <v>-55.740231000000001</v>
       </c>
       <c r="F22" s="8">
         <v>46278.845833333333</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J22" s="1"/>
       <c r="O22" s="4"/>
@@ -1473,17 +1478,17 @@
         <v>46278.851388888892</v>
       </c>
       <c r="C23" s="7"/>
-      <c r="D23" s="9">
-        <v>-22027397</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-40713665</v>
+      <c r="D23" s="7">
+        <v>-22.027397000000001</v>
+      </c>
+      <c r="E23">
+        <v>-40.713664999999999</v>
       </c>
       <c r="F23" s="8">
         <v>46278.059027777781</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J23" s="1"/>
     </row>
@@ -1537,7 +1542,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="B1" t="s">
         <v>58</v>
@@ -1569,17 +1574,17 @@
         <v>46278.854166666664</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="10">
-        <v>-22597612</v>
-      </c>
-      <c r="E2" s="10">
-        <v>-41719658</v>
+      <c r="D2" s="1">
+        <v>-22.597612000000002</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-41.719658000000003</v>
       </c>
       <c r="F2" s="6">
         <v>46278.852083333331</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1591,17 +1596,17 @@
         <v>46278.854166666664</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="10">
-        <v>-22116941</v>
-      </c>
-      <c r="E3" s="10">
-        <v>-39828007</v>
+      <c r="D3" s="1">
+        <v>-22.116941000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-39.828006999999999</v>
       </c>
       <c r="F3" s="6">
         <v>46277.680555555555</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1613,17 +1618,17 @@
         <v>46278.854166666664</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="10">
-        <v>-22843798</v>
-      </c>
-      <c r="E4" s="10">
-        <v>-43143887</v>
+      <c r="D4" s="1">
+        <v>-22.843798</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-43.143886999999999</v>
       </c>
       <c r="F4" s="6">
         <v>46278.850694444445</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1635,17 +1640,17 @@
         <v>46278.854166666664</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="10">
-        <v>-22870724</v>
-      </c>
-      <c r="E5" s="10">
-        <v>-43122807</v>
+      <c r="D5" s="1">
+        <v>-22.870723999999999</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-43.122807000000002</v>
       </c>
       <c r="F5" s="6">
         <v>46278.851388888892</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1657,17 +1662,17 @@
         <v>46278.854166666664</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="10">
-        <v>-23822506</v>
-      </c>
-      <c r="E6" s="10">
-        <v>-42883278</v>
+      <c r="D6" s="1">
+        <v>-23.822506000000001</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-42.883277999999997</v>
       </c>
       <c r="F6" s="6">
         <v>46276.554861111108</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1679,17 +1684,17 @@
         <v>46278.854166666664</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="10">
-        <v>-22422045</v>
-      </c>
-      <c r="E7" s="10">
-        <v>-39956585</v>
+      <c r="D7" s="1">
+        <v>-22.422045000000001</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-39.956584999999997</v>
       </c>
       <c r="F7" s="6">
         <v>46276.88958333333</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -1701,17 +1706,17 @@
         <v>46278.854166666664</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="10">
-        <v>-22860916</v>
-      </c>
-      <c r="E8" s="10">
-        <v>-43182495</v>
+      <c r="D8" s="1">
+        <v>-22.860916</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-43.182495000000003</v>
       </c>
       <c r="F8" s="6">
         <v>46278.852083333331</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1723,17 +1728,17 @@
         <v>46278.854166666664</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="10">
-        <v>-24776045</v>
-      </c>
-      <c r="E9" s="10">
-        <v>-42720772</v>
+      <c r="D9" s="1">
+        <v>-24.776045</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-42.720771999999997</v>
       </c>
       <c r="F9" s="6">
         <v>46278.365277777775</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I9" s="1"/>
     </row>
@@ -1745,17 +1750,17 @@
         <v>46278.854166666664</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="10">
-        <v>-24533880</v>
-      </c>
-      <c r="E10" s="10">
-        <v>-42475761</v>
+      <c r="D10" s="1">
+        <v>-24.53388</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-42.475760999999999</v>
       </c>
       <c r="F10" s="6">
         <v>46278.479861111111</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -1767,17 +1772,17 @@
         <v>46278.854166666664</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="10">
-        <v>-23314625</v>
-      </c>
-      <c r="E11" s="10">
-        <v>-43106281</v>
+      <c r="D11" s="1">
+        <v>-23.314624999999999</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-43.106281000000003</v>
       </c>
       <c r="F11" s="6">
         <v>46278.161805555559</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I11" s="1"/>
     </row>
@@ -1789,17 +1794,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C12" s="1"/>
-      <c r="D12" s="10">
-        <v>-21860369</v>
-      </c>
-      <c r="E12" s="10">
-        <v>-41020199</v>
+      <c r="D12" s="1">
+        <v>-21.860368999999999</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-41.020198999999998</v>
       </c>
       <c r="F12" s="6">
         <v>46278.861805555556</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I12" s="1"/>
     </row>
@@ -1811,17 +1816,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="10">
-        <v>-23740061</v>
-      </c>
-      <c r="E13" s="10">
-        <v>-42644466</v>
+      <c r="D13" s="1">
+        <v>-23.740061000000001</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-42.644466000000001</v>
       </c>
       <c r="F13" s="6">
         <v>46278.783333333333</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I13" s="1"/>
     </row>
@@ -1833,17 +1838,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="10">
-        <v>-25030201</v>
-      </c>
-      <c r="E14" s="10">
-        <v>-42652859</v>
+      <c r="D14" s="1">
+        <v>-25.030201000000002</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-42.652858999999999</v>
       </c>
       <c r="F14" s="6">
         <v>46277.406944444447</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1855,17 +1860,17 @@
         <v>46278.864583333336</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="10">
-        <v>-24566067</v>
-      </c>
-      <c r="E15" s="10">
-        <v>-42512630</v>
+      <c r="D15" s="1">
+        <v>-24.566067</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-42.512630000000001</v>
       </c>
       <c r="F15" s="6">
         <v>46278.536111111112</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -1904,12 +1909,13 @@
     <col min="7" max="7" width="15.88671875" customWidth="1"/>
     <col min="8" max="8" width="22.33203125" customWidth="1"/>
     <col min="9" max="9" width="23.109375" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" customWidth="1"/>
     <col min="11" max="11" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>58</v>
@@ -1941,17 +1947,17 @@
         <v>46278.857638888891</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="10">
-        <v>-22888233</v>
-      </c>
-      <c r="E2" s="10">
-        <v>-43215214</v>
+      <c r="D2" s="1">
+        <v>-22.888233</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-43.215214000000003</v>
       </c>
       <c r="F2" s="6">
         <v>46278.854166666664</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1963,17 +1969,17 @@
         <v>46278.857638888891</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="10">
-        <v>-24709820</v>
-      </c>
-      <c r="E3" s="10">
-        <v>-42413784</v>
+      <c r="D3" s="1">
+        <v>-24.709820000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-42.413784</v>
       </c>
       <c r="F3" s="6">
         <v>46278.55</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1985,17 +1991,17 @@
         <v>46278.857638888891</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="10">
-        <v>-22560759</v>
-      </c>
-      <c r="E4" s="10">
-        <v>-40122780</v>
+      <c r="D4" s="1">
+        <v>-22.560759000000001</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-40.122779999999999</v>
       </c>
       <c r="F4" s="6">
         <v>46276.90902777778</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -2007,17 +2013,17 @@
         <v>46278.857638888891</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="10">
-        <v>-22841331</v>
-      </c>
-      <c r="E5" s="10">
-        <v>-43134846</v>
+      <c r="D5" s="1">
+        <v>-22.841331</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-43.134846000000003</v>
       </c>
       <c r="F5" s="6">
         <v>46278.852083333331</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -2029,17 +2035,17 @@
         <v>46278.857638888891</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="10">
-        <v>-22375000</v>
-      </c>
-      <c r="E6" s="10">
-        <v>-40410228</v>
+      <c r="D6" s="1">
+        <v>-22.375</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-40.410227999999996</v>
       </c>
       <c r="F6" s="6">
         <v>46278.718055555553</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -2051,17 +2057,17 @@
         <v>46278.857638888891</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="10">
-        <v>-24543678</v>
-      </c>
-      <c r="E7" s="10">
-        <v>-42200840</v>
+      <c r="D7" s="1">
+        <v>-24.543678</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-42.200839999999999</v>
       </c>
       <c r="F7" s="6">
         <v>46278.672222222223</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -2073,17 +2079,17 @@
         <v>46278.857638888891</v>
       </c>
       <c r="C8" s="1"/>
-      <c r="D8" s="10">
-        <v>-21940434</v>
-      </c>
-      <c r="E8" s="10">
-        <v>-39786179</v>
+      <c r="D8" s="1">
+        <v>-21.940434</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-39.786178999999997</v>
       </c>
       <c r="F8" s="6">
         <v>46277.70416666667</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -2095,17 +2101,17 @@
         <v>46278.857638888891</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="10">
-        <v>-22798719</v>
-      </c>
-      <c r="E9" s="10">
-        <v>-40763451</v>
+      <c r="D9" s="1">
+        <v>-22.798718999999998</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-40.763451000000003</v>
       </c>
       <c r="F9" s="6">
         <v>46278.582638888889</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I9" s="1"/>
     </row>
@@ -2117,17 +2123,17 @@
         <v>46278.857638888891</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="10">
-        <v>-22953400</v>
-      </c>
-      <c r="E10" s="10">
-        <v>-40726486</v>
+      <c r="D10" s="1">
+        <v>-22.953399999999998</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-40.726486000000001</v>
       </c>
       <c r="F10" s="6">
         <v>46278.322916666664</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I10" s="1"/>
     </row>
@@ -2139,17 +2145,17 @@
         <v>46278.857638888891</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="10">
-        <v>-21967825</v>
-      </c>
-      <c r="E11" s="10">
-        <v>-39826687</v>
+      <c r="D11" s="1">
+        <v>-21.967825000000001</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-39.826687</v>
       </c>
       <c r="F11" s="6">
         <v>46278.853472222225</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I11" s="1"/>
     </row>
@@ -2161,17 +2167,17 @@
         <v>46278.85833333333</v>
       </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="9">
-        <v>-22861006</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-43178879</v>
+      <c r="D12" s="7">
+        <v>-22.861006</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-43.178879000000002</v>
       </c>
       <c r="F12" s="8">
         <v>46278.856249999997</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I12" s="1"/>
       <c r="N12" s="1"/>
@@ -2184,17 +2190,17 @@
         <v>46278.85833333333</v>
       </c>
       <c r="C13" s="7"/>
-      <c r="D13" s="9">
-        <v>-22862795</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-43167763</v>
+      <c r="D13" s="7">
+        <v>-22.862794999999998</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-43.167763000000001</v>
       </c>
       <c r="F13" s="8">
         <v>46278.856944444444</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I13" s="1"/>
       <c r="N13" s="1"/>
@@ -2207,17 +2213,17 @@
         <v>46278.85833333333</v>
       </c>
       <c r="C14" s="7"/>
-      <c r="D14" s="9">
-        <v>-23199171</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-43060268</v>
+      <c r="D14" s="7">
+        <v>-23.199171</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-43.060268000000001</v>
       </c>
       <c r="F14" s="8">
         <v>46275.845833333333</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -2229,17 +2235,17 @@
         <v>46278.85833333333</v>
       </c>
       <c r="C15" s="7"/>
-      <c r="D15" s="9">
-        <v>-22862747</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-43172367</v>
+      <c r="D15" s="7">
+        <v>-22.862746999999999</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-43.172367000000001</v>
       </c>
       <c r="F15" s="8">
         <v>46278.856944444444</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -2251,17 +2257,17 @@
         <v>46278.85833333333</v>
       </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="9">
-        <v>-24740973</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-42514408</v>
+      <c r="D16" s="7">
+        <v>-24.740973</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-42.514408000000003</v>
       </c>
       <c r="F16" s="8">
         <v>46278.145138888889</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I16" s="1"/>
     </row>
@@ -2273,17 +2279,17 @@
         <v>46278.85833333333</v>
       </c>
       <c r="C17" s="7"/>
-      <c r="D17" s="9">
-        <v>-26856745</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-48721401</v>
+      <c r="D17" s="7">
+        <v>-26.856745</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-48.721401</v>
       </c>
       <c r="F17" s="8">
         <v>46120.325694444444</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I17" s="1"/>
     </row>
@@ -2295,17 +2301,17 @@
         <v>46278.85833333333</v>
       </c>
       <c r="C18" s="7"/>
-      <c r="D18" s="9">
-        <v>-22862825</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-43161587</v>
+      <c r="D18" s="7">
+        <v>-22.862825000000001</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-43.161586999999997</v>
       </c>
       <c r="F18" s="8">
         <v>46278.856944444444</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I18" s="1"/>
     </row>
